--- a/backend/src/uploads/membership_data.xlsx
+++ b/backend/src/uploads/membership_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CMYK\ChelsField-Final\Chelsfield_Cricket_Club - Copy-old\backend\src\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CMYK\ChelsField-Final\Chelsfield-Cricket-Club\backend\src\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021F4321-311B-4369-B47F-EC7D7026C550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0D4ACE-ABC1-4BC6-BEAE-FB8E37333511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -432,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
@@ -473,8 +473,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:L1" numberStoredAsText="1"/>
   </ignoredErrors>
